--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_013/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_013/extracted.xlsx
@@ -280,6 +280,11 @@
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1331,12 +1336,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Steady-state CHT model for liquid-cooled cold plate to support design decisions on flow rate, TIM selection, and thermal margin to 85 C junction limit</t>
+          <t>Predict steady-state junction temperatures and pressure drop of a liquid-cooled cold plate for high-density power electronics design decisions</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>A conjugate heat transfer (CHT) model of a liquid-cooled aluminum cold plate managing up to 280 W from six electronic packages (four GaN inverter modules at 55 W each, two FPGAs at 10 W each) in an airborne power conversion unit. The model is used at the current design phase to screen candidate flow rates (1.2–1.8 L/min), rank uncertain parameters, and predict maximum junction temperature margin to the 85 C qualification limit under steady sea-level operation. Transient warm-up and altitude effects are outside scope.</t>
+          <t>A conjugate heat transfer (CHT) CFD model of a machined 6061-T6 aluminum cold plate with eight parallel serpentine channels is used to screen coolant flow rates, evaluate thermal margin to the 85 C junction temperature limit, and rank the leverage of uncertain parameters (TIM resistance, flow rate, heat load) for six electronic packages (four GaN inverter modules at 55 W each, two control FPGAs at 10 W each) totaling up to 280–300 W. The COU is steady-state operation at sea-level ambient, incompressible coolant, fixed inlet temperature in the range 20–35 C and flow rates 1.2–1.8 L/min. Transient warm-up, altitude effects, radiation, and external convection are excluded from the current COU scope.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1366,7 +1371,7 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>S. Ahmed, B. Cortez (prepared); R. Li, P. Nguyen (reviewed)</t>
+          <t>S. Ahmed, B. Cortez (analysts); reviewed by R. Li, P. Nguyen</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1374,9 +1379,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (CHT Model Credibility Assessment Report, Project CP-CHT-23A, dated 2026-08-06, prepared by Thermal/Fluids Analysis Group, Systems Integration Lab)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1505,7 +1510,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Maximum predicted device junction temperature must remain below 85 C under worst-case steady thermal boundary conditions; model must support go/no-go decision on cold-plate geometry freeze and TIM selection with sufficient accuracy for the current design phase.</t>
+          <t>Maximum predicted device junction temperature must remain below 85 C under worst-case steady-state thermal boundary conditions within the specified operating envelope (1.2–1.8 L/min, 20–35 C inlet, up to 300 W load); the model must support go/no-go decisions on cold-plate geometry freeze and TIM selection with sufficient predictive accuracy to resolve margin to this limit.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1527,12 +1532,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>CP-CHT-23A Conjugate Heat Transfer Model</t>
+          <t>CP-CHT-23A Conjugate Heat Transfer CFD Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Steady RANS (k-omega SST) CHT model of the cold plate and device stack in Ansys Fluent 2023 R1; includes solid conduction, internal coolant flow, and TIM layers; medium grid (3.8M fluid + 2.1M solid cells) used for design sweeps; fine grid (11.5M + 5.4M) used for spot-checks.</t>
+          <t>Steady RANS (k-omega SST) conjugate heat transfer model of the liquid-cooled cold plate in Ansys Fluent 2023 R1; includes solid domains (aluminum body, copper baseplates, solder stacks, TIM layers) and fluid domain (internal coolant passages); medium grid 3.8M fluid + 2.1M solid cells used for parametric sweeps; fine grid 11.5M + 5.4M cells used for spot-checks.</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1549,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Bench Validation Dataset (Points A and B)</t>
+          <t>Bench Measurement Dataset — Points A and B</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Two steady operating points measured on a benchtop loop: Point A (1.5 L/min, 25 C inlet, 240 W) and Point B (1.8 L/min, 35 C inlet, 300 W); five Type T thermocouples on device case tops, calibrated Coriolis flow meter, Validyne differential pressure transducer, NIST-traceable RTD reference; documented under Metrology Log MTL-CP-07.</t>
+          <t>Steady-state thermocouple case temperatures (five Type T sensors), inlet/outlet differential pressure (Validyne DP45), and flow rate (Bronkhorst Coriolis) measured at two operating points (Point A: 1.5 L/min, 25 C, 240 W; Point B: 1.8 L/min, 35 C, 300 W) after 30-minute thermal soak; calibration documented under Metrology Log MTL-CP-07.</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1566,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LHS Uncertainty Propagation Dataset</t>
+          <t>LHS Uncertainty Propagation Dataset (v0.9.2)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>120-run Latin Hypercube sample on medium grid varying flow rate, inlet temperature, heat load, TIM conductivity, TIM contact resistance, and aluminum conductivity; sparse polynomial chaos (LARS) surrogate fitted to decompose variance and produce 95% confidence intervals on T_j,max and pressure drop.</t>
+          <t>120-run Latin Hypercube sample on the medium grid spanning six input parameters (flow rate, inlet temperature, heat load, TIM conductivity, TIM contact resistance, aluminum k); sparse polynomial chaos (LARS) surrogate fitted for variance decomposition and 95% confidence interval estimation on T_j,max and pressure drop.</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1583,12 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Material Property Dataset</t>
+          <t>Material Properties Dataset</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Coolant (60/40 PGW) properties from ASHRAE Fundamentals 2017 correlations; aluminum 6061-T6 thermal conductivity measured via laser flash (NETZSCH LFA 467) on two coupons (mean 167 W/m-K, SD 3 W/m-K); copper and TIM properties from literature and vendor datasheet respectively; all documented in report Section 5 and Appendix A4.</t>
+          <t>Coolant (60/40 PGW) properties from ASHRAE Fundamentals 2017 correlations; aluminum 6061-T6 thermal conductivity measured by laser flash on two coupons (NETZSCH LFA 467, mean 167 W/m-K, std 3 W/m-K); copper literature value; TIM conductivity from vendor datasheet (Bergquist Gap Pad TGP 3000, 3.0–4.0 W/m-K); TIM thickness SPC data from assembly line trial.</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2040,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (coarse 2.0M, medium 5.9M, fine 16.9M total cells) evaluated at nominal operating point. T_j,max: 79.8 C (coarse), 78.9 C (medium), 78.6 C (fine). Pressure drop: 17.1, 18.6, 19.2 kPa. Richardson extrapolation with apparent order p≈1.9 (temperature) and p≈2.1 (pressure) yielded estimated grid influence on T_j,max of 0.7 K (1.9%) at medium grid; 0.9 kPa (4.8%) for pressure drop.</t>
+          <t>Three systematically refined meshes (coarse 2.0M, medium 5.9M, fine 16.9M total cells) at nominal operating point (1.5 L/min, 25 C, 240 W); QoIs monitored are T_j,max and pressure drop; refinement factor r ≈ 1.5; apparent order p ≈ 1.9 (temperature) and 2.1 (pressure).</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI estimate</t>
+          <t>Richardson extrapolation extrapolated solutions; coarse-to-medium and medium-to-fine changes</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2050,12 +2055,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation with apparent order estimation</t>
+          <t>Generalized Richardson extrapolation / GCI-type analysis</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Grid influence on T_j,max: 0.7 K (1.9%); on Δp: 0.9 kPa (4.8%)</t>
+          <t>Grid influence on T_j,max at medium grid: 0.7 K (1.9%); grid influence on Δp at medium grid: 0.9 kPa (4.8%); T_j,max change medium-to-fine: 0.3 K</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2067,7 +2072,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Study</t>
+          <t>Iterative Solver Convergence Check</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2077,12 +2082,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Convergence monitored via energy residuals (target &lt;1e-5, achieved by ~2800 iterations out of 4200 total), momentum and turbulence residuals (&lt;5e-5), mass imbalance (&lt;0.1%), T_j,max running average stabilized to &lt;0.1 K change over 500 iterations, outlet temperature stabilized within 0.02 C, and conjugate interface heat balance closed within 0.3%.</t>
+          <t>Monitoring of residuals, running average of T_j,max, outlet temperature stability, and integral heat balance across conjugate interface for all steady cases; convergence declared when energy residuals below 1e-5, momentum and turbulence below 5e-5, mass imbalance below 0.1%, T_j,max monitor stable to within 0.1 K over 500 iterations.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Prescribed convergence criteria</t>
+          <t>Prescribed convergence criteria; integral heat balance closure target</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2092,7 +2097,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Energy residual &lt;1e-5; mass imbalance &lt;0.1%; T_j,max drift &lt;0.1 K; heat balance closure 0.3%</t>
+          <t>Energy residual &lt;1e-5 at ~4200 iterations; mass imbalance &lt;0.1%; heat balance closed within 0.3%; outlet temperature stable within 0.02 C; T_j,max monitor stable within 0.1 K</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2104,7 +2109,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Bench Comparison — Point A (Nominal: 1.5 L/min, 25 C, 240 W)</t>
+          <t>Bench Comparison — Point A (1.5 L/min, 25 C, 240 W)</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2114,12 +2119,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Model predictions compared to benchtop measurements at Point A. Average case temperature (six devices): measured 71.8 C ± 0.3 C, predicted 71.0 C (fine) / 71.2 C (medium). Hottest junction: measured 79.5 C ± 0.6 C, predicted 78.6 C (fine) / 78.9 C (medium). Pressure drop: measured 18.1 kPa ± 0.2 kPa, predicted 19.2 kPa (fine) / 18.6 kPa (medium). Mean absolute deviation across six case sensors: 0.9 C.</t>
+          <t>Comparison of CFD-predicted case temperatures (six devices), hottest junction temperature, and inlet-to-outlet pressure drop against bench measurements at Point A after 30-minute thermal soak.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Calibrated thermocouple and differential pressure measurements (MTL-CP-07)</t>
+          <t>Bench measurements: case avg 71.8 C ± 0.3 C; hottest junction 79.5 C ± 0.6 C (derived); Δp 18.1 kPa ± 0.2 kPa</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2129,12 +2134,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Instrumentation uncertainty budget (RSS); combined thermocouple uncertainty ±0.3 C–0.6 C; flow ±0.8% reading; pressure ±0.5% FS</t>
+          <t>Instrumentation uncertainty budget (RSS); combined thermocouple system uncertainty ±0.3 C; pressure ±0.5% FS; flow ±0.8% reading</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Case temp MAD: 0.9 C; junction temp deviation: 0.9 C (fine); Δp deviation: 0.5 kPa (fine)</t>
+          <t>Case avg deviation: predicted 71.0 C (fine) vs 71.8 C measured; error 0.8 C (1.1%); junction: predicted 78.6 C vs 79.5 C; error 0.9 C (1.1%); Δp: predicted 19.2 kPa vs 18.1 kPa; error 1.1 kPa (6.1%); mean absolute deviation across six case sensors: 0.9 C</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2146,7 +2151,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Bench Comparison — Point B (Elevated: 1.8 L/min, 35 C, 300 W)</t>
+          <t>Bench Comparison — Point B (1.8 L/min, 35 C, 300 W)</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2156,12 +2161,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Model predictions compared to benchtop measurements at Point B. Average case temperature: measured 82.9 C ± 0.4 C, predicted 83.8 C (medium). Hottest junction: measured 90.7 C ± 0.8 C, predicted 92.1 C (medium). Pressure drop: measured 23.7 kPa ± 0.3 kPa, predicted 24.4 kPa (medium). Mean absolute deviation: 1.6 C. Larger discrepancy attributed to TIM voiding near clamp edge observed on teardown; model assumes uniform TIM.</t>
+          <t>Comparison of CFD-predicted case temperatures and pressure drop against bench measurements at Point B (overload condition, 300 W, 35 C inlet, 1.8 L/min); post-test teardown revealed TIM voiding at Device 3, explaining increased discrepancy.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Calibrated thermocouple and differential pressure measurements (MTL-CP-07)</t>
+          <t>Bench measurements: case avg 82.9 C ± 0.4 C; hottest junction 90.7 C ± 0.8 C (derived); Δp 23.7 kPa ± 0.3 kPa</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2171,12 +2176,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Instrumentation uncertainty budget (RSS)</t>
+          <t>Instrumentation uncertainty budget; same calibrated instrumentation as Point A</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Case temp MAD: 1.6 C; junction temp deviation: 1.4 C; Δp deviation: 0.7 kPa</t>
+          <t>Case avg: predicted 83.8 C vs 82.9 C; error 0.9 C (1.1%); junction: predicted 92.1 C vs 90.7 C; error 1.4 C (1.5%); Δp: predicted 24.4 kPa vs 23.7 kPa; error 0.7 kPa (3.0%); mean absolute deviation across six case sensors: 1.6 C</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2188,7 +2193,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Parametric Uncertainty and Sensitivity Sweep (LHS/PCE)</t>
+          <t>Parametric Uncertainty and Sensitivity Propagation (LHS + PCE)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2198,12 +2203,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>120-run Latin Hypercube sample on medium grid with six uncertain inputs propagated via sparse polynomial chaos (LARS). Variance decomposition for T_j,max: TIM contact resistance 54%, flow rate 28%, heat load 12%, remaining ≤6%. 95% prediction interval for T_j,max at nominal: 78.6 C ± 2.1 C (upper bound 80.7 C, 4.3 C below 85 C limit). Δp 95% interval: 18.6 ± 1.4 kPa. Overall 95% CI width for T_j,max under 4.5 K.</t>
+          <t>120-run Latin Hypercube sample on medium grid with six uncertain inputs propagated through sparse polynomial chaos (LARS) surrogate; variance decomposition and 95% prediction interval computed for T_j,max and Δp; dominant contributor identified as TIM effective contact resistance (54% of variance).</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>85 C junction temperature limit</t>
+          <t>Design requirement: T_j,max 95% upper bound must remain below 85 C at nominal conditions</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2213,12 +2218,12 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Sampling + sparse polynomial chaos expansion (LARS) with Sobol variance decomposition</t>
+          <t>Latin Hypercube Sampling (120 runs) with sparse PCE (LARS) surrogate; variance decomposition (Sobol indices)</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>95% CI width T_j,max: &lt;4.5 K; upper 95% bound: 80.7 C; margin to limit: 4.3 C</t>
+          <t>T_j,max 95% CI width: 4.5 K (±2.1 K about 78.6 C); upper 95% bound 80.7 C; margin to 85 C limit: ~4.3 C; TIM contact resistance accounts for 54% of variance; Δp 95% CI: 18.6 ± 1.4 kPa</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2372,12 +2377,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented version; case files version-controlled; reproducible setup</t>
+          <t>Commercial solver with documented quality processes; version-controlled case files; reproducible runs</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R1 (double precision, Linux build) is a widely used commercial CFD solver with vendor QA processes implied by its release designation. Case files are stored in a Git LFS repository (TPG/coldplate-cht) with tagged releases (v0.9.2, v1.0.0) and commit hashes for key files (e.g., cp_nominal_med.cas.h5 at commit 2f1a83c). A run manifest (runs.csv) captures random seeds and links result artifacts. No explicit vendor certification document or ISO 9001 reference is cited in the evidence, preventing a higher level.</t>
+          <t>Ansys Fluent 2023 R1 (double precision, Linux build) is a widely used commercial solver with vendor-maintained quality assurance. Case and data files are stored under Git LFS in repository TPG/coldplate-cht with explicit version tags (v0.9.2, v1.0.0) and commit hashes (e.g., commit 2f1a83c, 9e5a1d1). A run manifest (runs.csv) links random seeds and result artifacts. A templated README captures boundary conditions, solver controls, and mesh metrics per case folder. No explicit mention of ISO 9001 certification or formal regression test suite for Fluent itself, but commercial solver pedigree and version tracking are documented (report.md Section 7, appendix.md A5).</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2406,12 +2411,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code produces physically consistent results on benchmark or canonical problems</t>
+          <t>Evidence code solves governing equations correctly; internal benchmarks or references to solver validation</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>The report notes that the SST turbulence model with low-Re treatment was benchmarked on an internal straight-channel case to verify reasonable friction factors (Section 6). A laminar model comparison at the lowest flow setting showed physically expected behaviour (underprediction of Δp, overprediction of wall temperature by &gt;5 C), corroborating the turbulence model choice. No formal method of manufactured solutions (MMS) or published analytical benchmark comparison is documented; evidence is limited to an internal channel sanity check.</t>
+          <t>The report references a brief internal benchmark: the SST turbulence model with low-Re treatment was benchmarked on an internal straight-channel case to confirm reasonable friction factors (report.md Section 6). A laminar model comparison at the lowest flow setting showed physically expected behavior (underprediction of Δp, overprediction of wall temperature by &gt;5 C). No formal method of manufactured solutions, published benchmark suite, or code-level analytical comparison is documented. This provides basic corroborating evidence for the turbulence closure selection but does not constitute comprehensive numerical code verification.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2440,12 +2445,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified GCI or equivalent; grid influence on QoIs below acceptable threshold</t>
+          <t>Mesh convergence demonstrated with quantified GCI or equivalent; changes between levels within acceptable tolerance for QoIs</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes with refinement factor r≈1.5 were generated. Richardson extrapolation with apparent order p≈1.9 (temperature) and p≈2.1 (pressure) quantified grid influence on T_j,max as 0.7 K (1.9%) at medium grid and 0.9 kPa (4.8%) for Δp. Mesh quality metrics reported in Appendix A1 (min orthogonal quality 0.14 in elbows, max skewness 0.86 localised at junction). A sensitivity case with localised refinement at the low-quality region confirmed limited impact. Near-wall treatment verified with y+ targeting &lt;2 (medium) and &lt;1.2 (fine). Fine-grid spot-checks at two validation points provide additional confirmation.</t>
+          <t>Three systematically refined meshes (coarse, medium, fine; refinement factor r ≈ 1.5) were generated with boundary-layer inflation preserved. Richardson extrapolation was applied with apparent orders p ≈ 1.9 (temperature) and p ≈ 2.1 (pressure). Grid influence on T_j,max at medium grid quantified as 0.7 K (1.9%); on Δp as 0.9 kPa (4.8%). Mesh quality metrics are reported (min orthogonal quality 0.14 in manifold elbows, max skewness 0.86 localized at channel-to-manifold junction with sensitivity case confirming limited impact). Prism layer parameters and y+ targets documented. Fine grid used to spot-check two operating points. Quantified uncertainties are provided for both primary QoIs (report.md Section 3.1, appendix.md A1).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2474,12 +2479,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residuals meet prescribed targets; monitor quantities stabilised; integral balances close</t>
+          <t>Residuals meet defined targets; QoI monitors demonstrate convergence; integral balances close</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Convergence criteria documented: energy residuals &lt;1e-5 (achieved by ~2800 of 4200 iterations), momentum and turbulence &lt;5e-5, mass imbalance &lt;0.1%. Running average of T_j,max stabilised to &lt;0.1 K change over 500 iterations before convergence declaration; outlet temperature stabilised within 0.02 C. Conjugate interface heat balance closed within 0.3%. Solver settings (pseudo-transient CFL ramp 5→50, under-relaxation adjustments) fully documented in report Section 3.2 and Appendix A2.</t>
+          <t>Explicit convergence criteria are defined: energy residuals below 1e-5; momentum and turbulence below 5e-5; mass imbalance below 0.1%. Running monitor of T_j,max stabilized to &lt;0.1 K change over 500 iterations; outlet temperature stabilized within 0.02 C. Integral heat balance across conjugate interface closed within 0.3%. Solver settings are fully documented including pseudo-transient CFL ramping (5 to 50 over 2000 iterations), under-relaxation adjustments, and total iterations to convergence (~4200). Energy residual plateau behavior described (report.md Section 3.2, appendix.md A2).</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2508,12 +2513,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary conditions verified; mesh quality checked</t>
+          <t>Independent review of model setup; boundary condition verification; mesh quality confirmed; post-processing validated</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>A two-person setup review was held on 2026-07-18 (minutes filed as Q-REV-CHT-05), covering boundary conditions, solver controls, and mesh metrics. Reviewer comments led to increasing near-wall layers from 12 to 14 on the fine mesh and rechecking y+. A templated README per case folder documents boundary conditions and solver controls. A structured conceptual walk-through with electrical packaging and test teams (Section 6) confirmed physics representation. External heat loss was checked via a back-of-envelope calculation (Appendix A7). No formal independent third-party audit or checklist against a published standard is cited.</t>
+          <t>A two-person peer review of the setup was conducted on 2026-07-18 (minutes in Q-REV-CHT-05); reviewer comments led to increasing near-wall layers from 12 to 14 on the fine mesh and rechecking y+. Boundary conditions are documented (inlet mass flow, fixed inlet temperature, adiabatic outer walls, volumetric heat sources) and traceability to test chiller setpoints established. A structured walk-through with electrical packaging and test teams verified physical completeness of the model (Section 6). Hand calculations validated radiation and external convection neglect (report.md Sections 2.1, 6, 7). No independent parallel model or automated check scripts mentioned beyond the peer review.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2542,12 +2547,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations justified for the physics regime; turbulence model selection rationale provided; known limitations documented</t>
+          <t>Governing equations justified; turbulence model selection rationale provided; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady RANS (k-omega SST with low-Re corrections) chosen for internal cooling channels at Re≈2200–3200. Rationale provided: SST with low-Re treatment benchmarked on internal straight-channel case; laminar model comparison at lowest flow showed &gt;5 C over-prediction, supporting turbulence closure. Radiation neglected with hand-calculation justification (&lt;0.3 K impact). Buoyancy negligible relative to forced convection at these Re numbers. Adiabatic outer wall assumption supported by enclosure design and test rig insulation. Limitations documented (transitional effects at low flow, TIM uniformity assumption, no transient). Explicit citation of turbulence model validation literature is absent, capping the level.</t>
+          <t>Steady RANS with k-omega SST and low-Re corrections is justified for the transitional Reynolds number range (Re ≈ 2200–3200). The turbulence model choice is supported by an internal straight-channel benchmark confirming reasonable friction factors and a laminar comparison showing physically expected deviation at low flow (&gt;5 C over-prediction of wall temperature). Radiation and buoyancy are assessed by hand calculation and found negligible (&lt;0.3 K impact). Adiabatic external wall assumption is supported by a back-of-envelope calculation (0.3 W parasitic, &lt;0.1 C impact). Conjugate conduction paths are explicitly represented. Limitations are clearly documented: transient effects, altitude, TIM non-uniformity, and transitional turbulence effects at the low-flow bound (report.md Sections 2.2, 6, 10).</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2576,12 +2581,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from measurement or traceable sources; boundary conditions from calibrated instruments; input uncertainties characterised</t>
+          <t>Material properties from testing or traceable sources; boundary conditions from calibrated measurements; input uncertainty characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Aluminum k measured by laser flash on two coupons (mean 167 W/m-K, SD 3 W/m-K; NETZSCH LFA 467). Coolant properties from ASHRAE Fundamentals 2017 correlations over the valid temperature range. TIM conductivity from vendor datasheet (3.0–4.0 W/m-K); thickness tolerance from SPC assembly chart. Instrument calibrations documented under Metrology Log MTL-CP-07, all current within 6 months of test. Heat loads defined as uniform volumetric generation per device footprint. Inlet conditions matched to chiller setpoints with ±0.1 C control verified by NIST-traceable RTD. Input uncertainty ranges formally defined and propagated in the LHS sweep (Section 5.2 and Appendix A4).</t>
+          <t>Aluminum thermal conductivity measured by laser flash on two coupons (NETZSCH LFA 467): mean 167 W/m-K, std 3 W/m-K. Coolant properties from ASHRAE 2017 correlations with temperature-dependent functions validated over the use range (20–60 C); sensitivity check showed &lt;0.5 K impact of constant cp/k approximation. TIM conductivity range (3.0–4.0 W/m-K) from vendor datasheet; thickness tolerance from SPC assembly data. Boundary conditions (flow rate, inlet temperature) traced to calibrated chiller setpoints and Coriolis meter (±0.8%). Full instrumentation uncertainty budget documented (appendix.md A3). All six uncertain inputs were characterized with probability distributions for the UQ sweep. Metrology Log MTL-CP-07 documents calibration currency (within 6 months) for thermocouples and RTD (report.md Section 5, appendix.md A3–A4).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2610,12 +2615,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is representative of the design; assembly documented</t>
+          <t>Test article is representative of the design; sample characterization documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single benchtop cold plate assembly was tested at two operating points. TIM (Bergquist Gap Pad TGP 3000, 0.5 mm) installed per vendor instructions with calibrated torque screwdriver at 0.9 N·m. Post-test teardown revealed voiding at Device 3, confirming assembly variability. Only one physical specimen was tested; no statistical characterisation across multiple units or production-representative sampling is reported. Sample size is not explicitly justified beyond feasibility at this design phase.</t>
+          <t>A single production-representative benchtop cold plate assembly was tested at two operating points (Points A and B). The TIM (Bergquist Gap Pad TGP 3000) was installed per vendor instructions with clamp torque set to 0.9 N·m using a calibrated torque screwdriver. Post-test teardown at Point B revealed TIM voiding at Device 3, demonstrating the assembly was not perfectly defect-free. Only one physical article was tested; no statistical characterization across multiple specimens. The assembly uses the same materials and geometry as the CAD model (PLM item CP-112-B Rev B). For a design-phase engineering study this is adequate but limited (report.md Sections 4.1, 4.2).</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2644,12 +2649,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled environment; measurement uncertainty quantified; test standards referenced</t>
+          <t>Calibrated instruments; controlled environment; measurement uncertainty quantified; test standards followed</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Chiller (Julabo FP50) with ±0.1 C setpoint control verified by NIST-traceable RTD (Fluke 1523). Flow measured by Bronkhorst Coriolis CORI-FLOW at ±0.8% of reading. Differential pressure by Validyne DP45 at ±0.5% FS. Five Type T thermocouples with NI-9213 DAQ, system-level calibration yielding ±0.3 C combined uncertainty. All calibrations current within 6 months under Metrology Log MTL-CP-07. Instrumentation uncertainty budget (RSS) detailed in Appendix A3 (combined temperature uncertainty ±0.6 C including junction-to-case inferencing). Thermal soak of 30 minutes before data capture. External insulation used to match adiabatic boundary assumption.</t>
+          <t>Chiller setpoint control ±0.1 C verified with NIST-traceable RTD probe (Fluke 1523). Flow rate measured with Bronkhorst Coriolis mini CORI-FLOW ±0.8% of reading. Pressure measured with Validyne DP45 ±0.5% FS over 35 kPa range. Five Type T thermocouples with NI-9213 DAQ, system-level calibration ±0.3 C combined uncertainty. Full instrumentation uncertainty budget documented using RSS combination (appendix.md A3). All calibrations current within 6 months of test (Metrology Log MTL-CP-07). Thermal soak of 30 minutes before data collection. Two distinct operating points tested. Test rig matched adiabatic enclosure assumption with foam insulation. Pressure tap placement documented (1/8" NPT ports at inlet and outlet manifolds).</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2678,12 +2683,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs shown to match experimental conditions; measurement uncertainties propagated into comparison</t>
+          <t>Model inputs explicitly matched to experimental conditions; measurement uncertainty propagated into comparison</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions set to match test chiller setpoints and flow meter readings at Points A and B. Pressure outlet reference matched to tap configuration. Heat loads in model set to match device power ratings applied in test. TIM properties in model set to vendor nominal (3.5 W/m-K) matching installed product. Temperature comparison accounts for thermocouple footprint locations by post-processing model surface nodes at equivalent positions. Measurement uncertainties (±0.3 C case temperature, ±0.6 C junction-derived) are reported alongside predictions, enabling direct overlap assessment. No formal uncertainty propagation from input parameter mismatch to output comparison is conducted separately from the broader LHS sweep.</t>
+          <t>Model boundary conditions were set to match test chiller setpoints (25 C and 35 C inlet) and flow meter readings (1.5 and 1.8 L/min). Heat loads were set to match the applied electrical power (240 W at Point A, 300 W at Point B). TIM properties (3.5 W/m-K nominal, 0.5 mm thickness, contact resistance 0.9 N·m torque) matched vendor installation. Model post-processing was performed at thermocouple footprint locations (solid surface nodes) and junction depth (1.0 mm below case surface) to match measurement points. Instrument uncertainties (±0.3 C temperature, ±0.8% flow, ±0.5% FS pressure) were documented and used to frame comparison tolerances. The junction-to-case temperature rise was derived from the model conduction path, with a ±0.5 C additional inferencing uncertainty acknowledged (appendix.md A3). No explicit formal input parameter comparison table, but matching is described per case (report.md Sections 4.1, 4.2).</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2712,12 +2717,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative error metrics reported at multiple comparison points; model predictions within measurement uncertainty or deviation explained physically</t>
+          <t>Quantitative error metrics across multiple comparison points; uncertainty bands on both experiment and prediction; systematic analysis of discrepancies</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison at two operating points: Point A case temperature MAD 0.9 C (six sensors), junction temperature deviation 0.9 C (fine grid vs. 79.5 C ± 0.6 C measured); Δp deviation 0.5 kPa vs. 18.1 ± 0.2 kPa. Point B case temperature MAD 1.6 C, junction deviation 1.4 C, Δp 0.7 kPa. Larger Point B discrepancy attributed to observed TIM voiding, providing a physically grounded explanation rather than unexplained bias. Mean absolute deviation reported across all six case sensors at both points. 95% confidence intervals from UQ sweep show upper bound 80.7 C vs. 85 C limit. Qualitative corroboration from IR thermography showing consistent spatial hot-spot pattern (Appendix A6). Pressure drop comparison also included at both points.</t>
+          <t>Quantitative comparisons provided at two operating points for three QoIs (case temperature average, hottest junction temperature, pressure drop). Point A: case avg error 0.8 C (1.1%), junction error 0.9 C (1.1%), Δp error 1.1 kPa (6.1%); mean absolute deviation across six sensors 0.9 C. Point B: case avg error 0.9 C (1.1%), junction error 1.4 C (1.5%), Δp error 0.7 kPa (3.0%); mean absolute deviation 1.6 C. Experimental uncertainties quantified (±0.3–0.6 C temperature, ±0.2–0.3 kPa pressure). Both medium and fine grid predictions reported at Point A, enabling grid-vs-experiment decomposition. Physical explanation provided for larger Point B discrepancy (TIM voiding confirmed on teardown). 95% prediction interval from UQ sweep (±2.1 K, width 4.5 K) also reported. Qualitative IR thermal map corroboration noted (report.md Sections 4.2, 5.2, 8).</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2746,12 +2751,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model QoIs directly address the safety/performance decision; QoIs measurable both computationally and experimentally</t>
+          <t>QoIs directly address the safety and performance decision; measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Primary QoI T_j,max directly maps to the 85 C junction temperature qualification limit stated in the COU. Secondary QoI Δp directly supports pump sizing and flow verification. Both QoIs are computed by the model and measured (or derived) from bench instrumentation at the same operating conditions. The sensitivity study demonstrates T_j,max is the binding constraint and identifies the dominant contributing parameters, further confirming relevance. Case temperature average serves as an intermediate verification QoI bridging model output to directly measurable thermocouple data, with the junction-to-case rise derived from the model's internal conduction path.</t>
+          <t>The primary QoI is T_j,max (maximum device junction temperature), directly tied to the 85 C qualification limit. Secondary QoI is pressure drop (Δp), relevant to pump sizing and flow adequacy. Both QoIs are predicted by the model and were measured (or derived) experimentally. Junction temperature is derived from case surface measurements plus the conduction path model, which is an explicit part of the CHT model geometry. The uncertainty sweep ranks the inputs by their contribution to T_j,max variance, directly informing the design decisions (TIM selection, clamp torque, flow rate setting). Average case temperature is also compared as a corroborating metric. The QoIs are directly connected to the stated COU decisions: geometry freeze, TIM selection, pump sizing (report.md Sections 1, 8, 9, 11).</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2780,12 +2785,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions bracket the intended operating envelope; physics regime matches COU; gaps identified and bounded</t>
+          <t>Validation conditions span the intended operating envelope; same geometry, physics regime, and loading as the COU</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation was performed at two points (25 C / 1.5 L/min / 240 W and 35 C / 1.8 L/min / 300 W) that bracket the design operating range (20–35 C inlet, 1.2–1.8 L/min, up to 300 W), directly matching the stated COU envelope. The same geometry, coolant, and device configuration as the design are used. Steady-state physics match the current COU scope. Known gaps acknowledged: (1) transient operation not validated; (2) altitude/derating effects not covered; (3) fine-grid uncertainty propagation not performed (medium grid surrogate used); (4) only one specimen tested, limiting assembly-variability coverage. These limitations are explicitly documented in Section 10 with planned follow-on activities, preventing a higher level.</t>
+          <t>The two validation points (Point A: nominal 1.5 L/min, 25 C, 240 W; Point B: 1.8 L/min, 35 C, 300 W) bracket portions of the COU operating envelope (1.2–1.8 L/min, 20–35 C, up to 300 W). The same cold plate geometry, TIM, and device configuration as the design model are used. The same turbulence regime (transitional Re ≈ 2200–3200) is covered. However, the lower bound of the flow envelope (1.2 L/min) is not directly validated experimentally; the UQ sweep covers it parametrically. Transient operation, altitude effects, and external convection are explicitly excluded and acknowledged as limitations. Radiation is justified as negligible by hand calculation. The gap at the low-flow corner and overload regime is noted and limits the applicability statement accordingly. The evidence is adequate for the stated COU decisions at nominal and near-nominal conditions (report.md Sections 1, 4, 10, 11).</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2970,7 +2975,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model CP-CHT-23A is accepted for the stated context of use: screening candidate flow rates within 1.2–1.8 L/min, evaluating junction temperature margin to the 85 C limit under nominal steady conditions, and prioritising interface improvements based on sensitivity results. Evidence supporting acceptance includes: mesh convergence with quantified grid influence &lt;2% on T_j,max; stable iterative convergence with closed integral balances; bench validation at two operating points with mean absolute deviation under 2 K and physically explained residual bias; traceable material property and instrument data; and a structured uncertainty propagation yielding a 95% upper bound of 80.7 C with 4.3 C margin to the limit. Acceptance conditions: (a) the model must not be used for pass/fail judgements at overload conditions beyond the validated envelope (&gt;300 W or &gt;35 C inlet); (b) transient thermal predictions require a separate validation activity once duty cycle data are available; (c) any change to TIM specification or clamp torque outside the sampled range requires reassessment of the dominant uncertainty contributor.</t>
+          <t>The CHT model CP-CHT-23A is accepted for the stated context of use: screening candidate flow rates in the range 1.2–1.8 L/min, evaluating thermal margin to the 85 C junction temperature limit under steady nominal conditions, and ranking interface improvement priorities (TIM spec, clamp torque). The evidence base includes: quantified mesh convergence (GCI-type analysis showing &lt;2% temperature sensitivity), demonstrated iterative solver convergence with integral heat balance closure within 0.3%, direct bench validation at two operating points with mean absolute deviation below 1.6 C against calibrated instrumentation, and a structured 120-run LHS uncertainty propagation showing a 95% upper bound of 80.7 C against the 85 C limit (4.3 C margin). Conditions recorded: (1) The model must not be used for pass/fail judgements at overload conditions (&gt;300 W, &gt;35 C inlet) or conditions outside the validated envelope without further validation. (2) Transient thermal responses are outside the current COU and require a separate assessment once the controller duty cycle is finalized. (3) TIM voiding effects (as observed at Point B teardown) are not modeled; spatially variable contact resistance should be incorporated if hot-spot refinement is needed for final qualification. (4) The low-flow corner (1.2 L/min) has not been experimentally validated and relies on parametric extrapolation only.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2980,7 +2985,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>S. Ahmed, B. Cortez (prepared); R. Li, P. Nguyen (reviewed)</t>
+          <t>S. Ahmed, B. Cortez (analysts); R. Li, P. Nguyen (reviewers)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
